--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
@@ -51,12 +51,12 @@
     <t xml:space="preserve">Pozo Almonte</t>
   </si>
   <si>
+    <t xml:space="preserve">Colchane</t>
+  </si>
+  <si>
     <t xml:space="preserve">Camiña</t>
   </si>
   <si>
-    <t xml:space="preserve">Colchane</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:33</t>
+    <t xml:space="preserve">2026-09-09 23:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -581,7 +581,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -594,7 +594,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:31</t>
+    <t xml:space="preserve">2026-09-17 14:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
@@ -51,12 +51,12 @@
     <t xml:space="preserve">Pozo Almonte</t>
   </si>
   <si>
+    <t xml:space="preserve">Camiña</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colchane</t>
   </si>
   <si>
-    <t xml:space="preserve">Camiña</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:25</t>
+    <t xml:space="preserve">2026-09-23 12:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -581,9 +581,11 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1403</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>1402</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
@@ -594,9 +596,11 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1402</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>1403</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:53</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -680,7 +677,7 @@
         <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-02 11:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:26</t>
+    <t xml:space="preserve">2026-10-02 15:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:14</t>
+    <t xml:space="preserve">2026-10-05 12:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
